--- a/响应面-实验编号-参数表.xlsx
+++ b/响应面-实验编号-参数表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20752" windowHeight="9555"/>
+    <workbookView windowWidth="24750" windowHeight="12790"/>
   </bookViews>
   <sheets>
     <sheet name="实验编号-参数表" sheetId="1" r:id="rId1"/>
@@ -184,14 +184,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -647,148 +640,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1141,13 +1134,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="2" width="9.24778761061947" customWidth="1"/>
-    <col min="3" max="3" width="10.4513274336283" customWidth="1"/>
-    <col min="4" max="4" width="10.3185840707965" customWidth="1"/>
-    <col min="5" max="5" width="11.4513274336283" customWidth="1"/>
-    <col min="6" max="6" width="18.1061946902655" customWidth="1"/>
+    <col min="1" max="2" width="9.24545454545455" customWidth="1"/>
+    <col min="3" max="3" width="10.4545454545455" customWidth="1"/>
+    <col min="4" max="4" width="10.3181818181818" customWidth="1"/>
+    <col min="5" max="5" width="11.4545454545455" customWidth="1"/>
+    <col min="6" max="6" width="18.1090909090909" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1178,16 +1171,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="D2">
         <v>250</v>
       </c>
       <c r="E2">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F2">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1198,16 +1191,16 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="D3">
         <v>250</v>
       </c>
       <c r="E3">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F3">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1218,16 +1211,16 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="D4">
         <v>500</v>
       </c>
       <c r="E4">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F4">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1238,16 +1231,16 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="D5">
         <v>500</v>
       </c>
       <c r="E5">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F5">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1258,16 +1251,16 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="D6">
         <v>250</v>
       </c>
       <c r="E6">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F6">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1278,16 +1271,16 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="D7">
         <v>250</v>
       </c>
       <c r="E7">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F7">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1298,16 +1291,16 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="D8">
         <v>500</v>
       </c>
       <c r="E8">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F8">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1318,16 +1311,16 @@
         <v>7</v>
       </c>
       <c r="C9">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="D9">
         <v>500</v>
       </c>
       <c r="E9">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F9">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1338,16 +1331,16 @@
         <v>7</v>
       </c>
       <c r="C10">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="D10">
         <v>250</v>
       </c>
       <c r="E10">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F10">
-        <v>5000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1358,16 +1351,16 @@
         <v>7</v>
       </c>
       <c r="C11">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="D11">
         <v>250</v>
       </c>
       <c r="E11">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F11">
-        <v>5000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1378,16 +1371,16 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="D12">
         <v>500</v>
       </c>
       <c r="E12">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F12">
-        <v>5000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1398,16 +1391,16 @@
         <v>7</v>
       </c>
       <c r="C13">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="D13">
         <v>500</v>
       </c>
       <c r="E13">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F13">
-        <v>5000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1418,16 +1411,16 @@
         <v>7</v>
       </c>
       <c r="C14">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="D14">
         <v>250</v>
       </c>
       <c r="E14">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F14">
-        <v>5000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1438,16 +1431,16 @@
         <v>7</v>
       </c>
       <c r="C15">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="D15">
         <v>250</v>
       </c>
       <c r="E15">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F15">
-        <v>5000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1458,16 +1451,16 @@
         <v>7</v>
       </c>
       <c r="C16">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="D16">
         <v>500</v>
       </c>
       <c r="E16">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F16">
-        <v>5000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1478,16 +1471,16 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="D17">
         <v>500</v>
       </c>
       <c r="E17">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F17">
-        <v>5000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1498,16 +1491,16 @@
         <v>24</v>
       </c>
       <c r="C18">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="D18">
         <v>375</v>
       </c>
       <c r="E18">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="F18">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1518,16 +1511,16 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="D19">
         <v>375</v>
       </c>
       <c r="E19">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="F19">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1538,16 +1531,16 @@
         <v>24</v>
       </c>
       <c r="C20">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D20">
         <v>250</v>
       </c>
       <c r="E20">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="F20">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1558,16 +1551,16 @@
         <v>24</v>
       </c>
       <c r="C21">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D21">
         <v>500</v>
       </c>
       <c r="E21">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="F21">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1578,16 +1571,16 @@
         <v>24</v>
       </c>
       <c r="C22">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D22">
         <v>375</v>
       </c>
       <c r="E22">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="F22">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1598,16 +1591,16 @@
         <v>24</v>
       </c>
       <c r="C23">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D23">
         <v>375</v>
       </c>
       <c r="E23">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F23">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1618,16 +1611,16 @@
         <v>24</v>
       </c>
       <c r="C24">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D24">
         <v>375</v>
       </c>
       <c r="E24">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="F24">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1638,16 +1631,16 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D25">
         <v>375</v>
       </c>
       <c r="E25">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="F25">
-        <v>5000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1658,7 +1651,7 @@
         <v>33</v>
       </c>
       <c r="C26">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D26">
         <v>375</v>
@@ -1667,7 +1660,7 @@
         <v>0.025</v>
       </c>
       <c r="F26">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1678,7 +1671,7 @@
         <v>33</v>
       </c>
       <c r="C27">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D27">
         <v>375</v>
@@ -1687,7 +1680,7 @@
         <v>0.025</v>
       </c>
       <c r="F27">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1698,7 +1691,7 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D28">
         <v>375</v>
@@ -1707,7 +1700,7 @@
         <v>0.025</v>
       </c>
       <c r="F28">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1718,7 +1711,7 @@
         <v>33</v>
       </c>
       <c r="C29">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D29">
         <v>375</v>
@@ -1727,7 +1720,7 @@
         <v>0.025</v>
       </c>
       <c r="F29">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1738,7 +1731,7 @@
         <v>33</v>
       </c>
       <c r="C30">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D30">
         <v>375</v>
@@ -1747,7 +1740,7 @@
         <v>0.025</v>
       </c>
       <c r="F30">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1758,7 +1751,7 @@
         <v>33</v>
       </c>
       <c r="C31">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D31">
         <v>375</v>
@@ -1767,7 +1760,7 @@
         <v>0.025</v>
       </c>
       <c r="F31">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1778,7 +1771,7 @@
         <v>33</v>
       </c>
       <c r="C32">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D32">
         <v>375</v>
@@ -1787,7 +1780,7 @@
         <v>0.025</v>
       </c>
       <c r="F32">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
   </sheetData>
@@ -1800,7 +1793,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
